--- a/assets/excel/IPCse - Series históricas.xlsx
+++ b/assets/excel/IPCse - Series históricas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomasejberowicz/Library/CloudStorage/Dropbox/IPC seasonal adjustment/IPCse/Series Historicas - 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomasejberowicz/Documents/mrozada.github.io/assets/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ED3D76-7178-FD40-ACAE-86D5FA07E969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED9D2D4-D843-3042-BB8D-ED0971AEBBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índices" sheetId="1" r:id="rId1"/>
@@ -931,6 +931,24 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -942,12 +960,6 @@
     <xf numFmtId="2" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -960,22 +972,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1303,57 +1303,57 @@
   <sheetData>
     <row r="1" spans="2:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="5"/>
       <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="55" t="s">
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="57"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
       <c r="V3" s="8" t="s">
         <v>37</v>
       </c>
@@ -8963,68 +8963,68 @@
         <v>11701.76154</v>
       </c>
     </row>
-    <row r="121" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B121" s="44">
+    <row r="121" spans="2:22" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="50">
         <v>46235</v>
       </c>
-      <c r="C121" s="45">
+      <c r="C121" s="51">
         <v>12326.85071165153</v>
       </c>
-      <c r="D121" s="46">
+      <c r="D121" s="52">
         <v>12354.38410346925</v>
       </c>
-      <c r="E121" s="46">
+      <c r="E121" s="52">
         <v>12303.51165271639</v>
       </c>
-      <c r="F121" s="46">
+      <c r="F121" s="52">
         <v>12446.419430404731</v>
       </c>
-      <c r="G121" s="46">
+      <c r="G121" s="52">
         <v>12507.984564654011</v>
       </c>
-      <c r="H121" s="46">
+      <c r="H121" s="52">
         <v>12369.847178362421</v>
       </c>
-      <c r="I121" s="47">
+      <c r="I121" s="54">
         <v>12304.24065614342</v>
       </c>
-      <c r="J121" s="46">
+      <c r="J121" s="53">
         <v>13121.2544</v>
       </c>
-      <c r="K121" s="46">
+      <c r="K121" s="52">
         <v>8502.1206999999995</v>
       </c>
-      <c r="L121" s="46">
+      <c r="L121" s="52">
         <v>8496.46819704275</v>
       </c>
-      <c r="M121" s="46">
+      <c r="M121" s="52">
         <v>13885.4923</v>
       </c>
-      <c r="N121" s="46">
+      <c r="N121" s="52">
         <v>9793.6862000000001</v>
       </c>
-      <c r="O121" s="46">
+      <c r="O121" s="52">
         <v>13981.776664136931</v>
       </c>
-      <c r="P121" s="46">
+      <c r="P121" s="52">
         <v>12965.1212</v>
       </c>
-      <c r="Q121" s="46">
+      <c r="Q121" s="52">
         <v>11449.470499999999</v>
       </c>
-      <c r="R121" s="46">
+      <c r="R121" s="52">
         <v>11084.102999999999</v>
       </c>
-      <c r="S121" s="46">
+      <c r="S121" s="52">
         <v>11307.070560235319</v>
       </c>
-      <c r="T121" s="46">
+      <c r="T121" s="52">
         <v>15196.1764</v>
       </c>
-      <c r="U121" s="47">
+      <c r="U121" s="54">
         <v>12088.779942112231</v>
       </c>
-      <c r="V121" s="45">
+      <c r="V121" s="51">
         <v>11874.241119132061</v>
       </c>
     </row>
@@ -9054,57 +9054,57 @@
   <sheetData>
     <row r="1" spans="2:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="5"/>
       <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="55" t="s">
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="57"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
       <c r="V3" s="8" t="s">
         <v>37</v>
       </c>
@@ -16768,29 +16768,29 @@
   <sheetData>
     <row r="1" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
       <c r="I3" s="19" t="s">
         <v>3</v>
       </c>
@@ -16799,16 +16799,16 @@
       <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="74">
         <v>2026</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="68">
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="74">
         <v>2026</v>
       </c>
-      <c r="H4" s="69"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="19" t="str">
         <f>+_xlfn.CONCAT(H5, " ", C4, "/", H5, " ", C4-1)</f>
         <v>Ago. 2026/Ago. 2025</v>
@@ -16863,16 +16863,16 @@
       </c>
     </row>
     <row r="7" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="75"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="27" t="s">
@@ -17041,16 +17041,16 @@
       <c r="I14" s="29"/>
     </row>
     <row r="15" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B16" s="27" t="s">
@@ -17375,16 +17375,16 @@
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="72"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" s="27" t="s">
@@ -17569,16 +17569,16 @@
       </c>
     </row>
     <row r="37" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="64" t="s">
+      <c r="B37" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="1"/>
@@ -17627,16 +17627,16 @@
   <sheetData>
     <row r="1" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="33"/>
@@ -17666,11 +17666,11 @@
       <c r="B4" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="42"/>
       <c r="I4" s="26"/>
     </row>
@@ -18023,16 +18023,16 @@
       <c r="I18" s="41"/>
     </row>
     <row r="19" spans="2:9" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="36" t="s">
@@ -18373,16 +18373,16 @@
       </c>
     </row>
     <row r="33" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="76" t="s">
+      <c r="B33" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="4">
